--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487113_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487113_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7566</v>
+        <v>8.4861</v>
       </c>
       <c r="E2" t="n">
-        <v>11.4805</v>
+        <v>9.236700000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7239</v>
+        <v>-0.7507</v>
       </c>
       <c r="G2" t="n">
         <v>6.7545</v>
@@ -610,13 +610,13 @@
         <v>1.3511</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9441</v>
+        <v>1.6736</v>
       </c>
       <c r="T2" t="n">
-        <v>4.2119</v>
+        <v>1.9681</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2677</v>
+        <v>-0.2945</v>
       </c>
       <c r="V2" t="n">
         <v>-0.3281</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9958</v>
+        <v>5.6565</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4505</v>
+        <v>4.5128</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5452</v>
+        <v>1.1437</v>
       </c>
       <c r="G3" t="n">
         <v>4.329</v>
@@ -688,13 +688,13 @@
         <v>1.5441</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4038</v>
+        <v>2.0646</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4019</v>
+        <v>1.6604</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8057</v>
+        <v>0.4042</v>
       </c>
       <c r="V3" t="n">
         <v>0.614</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4619</v>
+        <v>4.371</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6926</v>
+        <v>5.0932</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2308</v>
+        <v>-0.7221</v>
       </c>
       <c r="G4" t="n">
         <v>2.6337</v>
@@ -766,13 +766,13 @@
         <v>0.965</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3153</v>
+        <v>0.5939</v>
       </c>
       <c r="T4" t="n">
-        <v>0.7549</v>
+        <v>1.1554</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0702</v>
+        <v>-0.5615</v>
       </c>
       <c r="V4" t="n">
         <v>1.1435</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>O. IBARROLA ITURRIA</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.2692</v>
+        <v>3.416</v>
       </c>
       <c r="E5" t="n">
-        <v>1.3469</v>
+        <v>2.2859</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9222</v>
+        <v>1.1301</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5392</v>
+        <v>-0.0883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7338</v>
+        <v>0.7399</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8054</v>
+        <v>-0.8283</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9376</v>
+        <v>0.5381</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1606</v>
+        <v>0.9208</v>
       </c>
       <c r="L5" t="n">
-        <v>1.0982</v>
+        <v>-0.3827</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6016</v>
+        <v>-0.6264</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8944</v>
+        <v>-0.1808</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2928</v>
+        <v>-0.4456</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.965</v>
+        <v>-0.193</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.9301</v>
       </c>
       <c r="R5" t="n">
-        <v>0.965</v>
+        <v>1.7371</v>
       </c>
       <c r="S5" t="n">
-        <v>3.3512</v>
+        <v>1.8977</v>
       </c>
       <c r="T5" t="n">
-        <v>2.9956</v>
+        <v>1.8782</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3556</v>
+        <v>0.0194</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6562</v>
+        <v>1.7997</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.6562</v>
+        <v>1.7997</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.1027</v>
+        <v>2.6682</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7852</v>
+        <v>1.3016</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3175</v>
+        <v>1.3666</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0883</v>
+        <v>2.1139</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7399</v>
+        <v>0.9058</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8283</v>
+        <v>1.2081</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5381</v>
+        <v>1.3729</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9208</v>
+        <v>0.5589</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3827</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6264</v>
+        <v>0.741</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1808</v>
+        <v>0.3469</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4456</v>
+        <v>0.3941</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.193</v>
+        <v>0.772</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7371</v>
+        <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5844</v>
+        <v>0.4386</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3775</v>
+        <v>0.585</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2068</v>
+        <v>-0.1464</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7997</v>
+        <v>-0.6562</v>
       </c>
       <c r="W6" t="n">
-        <v>1.7997</v>
+        <v>-0.6562</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>O. IBARROLA ITURRIA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7841</v>
+        <v>2.1339</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1852</v>
+        <v>0.1046</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5989</v>
+        <v>2.0293</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6225000000000001</v>
+        <v>1.5392</v>
       </c>
       <c r="H7" t="n">
-        <v>2.4768</v>
+        <v>0.7338</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.8543</v>
+        <v>0.8054</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7148</v>
+        <v>0.9376</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1953</v>
+        <v>-0.1606</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.4805</v>
+        <v>1.0982</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.09229999999999999</v>
+        <v>0.6016</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2815</v>
+        <v>0.8944</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.3738</v>
+        <v>-0.2928</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>-0.965</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.965</v>
+        <v>-1.9301</v>
       </c>
       <c r="R7" t="n">
         <v>0.965</v>
       </c>
       <c r="S7" t="n">
-        <v>3.3895</v>
+        <v>2.216</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1496</v>
+        <v>1.7533</v>
       </c>
       <c r="U7" t="n">
-        <v>1.24</v>
+        <v>0.4627</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.228</v>
+        <v>-0.6562</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2859</v>
+        <v>-0.6562</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.5138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.3876</v>
+        <v>1.8005</v>
       </c>
       <c r="E8" t="n">
-        <v>1.1013</v>
+        <v>1.8441</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2863</v>
+        <v>-0.0436</v>
       </c>
       <c r="G8" t="n">
-        <v>2.1139</v>
+        <v>0.6225000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9058</v>
+        <v>2.4768</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2081</v>
+        <v>-1.8543</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3729</v>
+        <v>0.7148</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5589</v>
+        <v>1.1953</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8139999999999999</v>
+        <v>-0.4805</v>
       </c>
       <c r="M8" t="n">
-        <v>0.741</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3469</v>
+        <v>1.2815</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3941</v>
+        <v>-1.3738</v>
       </c>
       <c r="P8" t="n">
-        <v>0.772</v>
+        <v>-0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R8" t="n">
-        <v>0.772</v>
+        <v>0.965</v>
       </c>
       <c r="S8" t="n">
-        <v>0.158</v>
+        <v>2.406</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3847</v>
+        <v>1.8085</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2267</v>
+        <v>0.5975</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6562</v>
+        <v>-1.228</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.6562</v>
+        <v>0.2859</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.5138</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4939</v>
+        <v>1.1146</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4773</v>
+        <v>1.1783</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0166</v>
+        <v>-0.06370000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>0.012</v>
@@ -1156,13 +1156,13 @@
         <v>0.193</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2888</v>
+        <v>0.9095</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3424</v>
+        <v>0.3586</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6312</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. ALVES DE SOUZA SILVA</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3002</v>
+        <v>0.5913</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1578</v>
+        <v>0.5194</v>
       </c>
       <c r="F10" t="n">
-        <v>0.458</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2143</v>
+        <v>2.1906</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08069999999999999</v>
+        <v>2.9839</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1335</v>
+        <v>-0.7933</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0207</v>
+        <v>2.7307</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0207</v>
+        <v>3.3583</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.6276</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1936</v>
+        <v>-0.5401</v>
       </c>
       <c r="N10" t="n">
-        <v>0.06</v>
+        <v>-0.3744</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1335</v>
+        <v>-0.1657</v>
       </c>
       <c r="P10" t="n">
-        <v>0.193</v>
+        <v>-2.3161</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-3.8602</v>
       </c>
       <c r="R10" t="n">
-        <v>0.193</v>
+        <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1071</v>
+        <v>0.431</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1785</v>
+        <v>1.363</v>
       </c>
       <c r="U10" t="n">
-        <v>0.07140000000000001</v>
+        <v>-0.9320000000000001</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>T. ALVES DE SOUZA SILVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.163</v>
+        <v>0.4073</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5194</v>
+        <v>-0.1578</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3564</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>2.1906</v>
+        <v>0.2143</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9839</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7933</v>
+        <v>0.1335</v>
       </c>
       <c r="J11" t="n">
-        <v>2.7307</v>
+        <v>0.0207</v>
       </c>
       <c r="K11" t="n">
-        <v>3.3583</v>
+        <v>0.0207</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6276</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.5401</v>
+        <v>0.1936</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3744</v>
+        <v>0.06</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1657</v>
+        <v>0.1335</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3161</v>
+        <v>0.193</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.8602</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.5441</v>
+        <v>0.193</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0026</v>
+        <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.363</v>
+        <v>-0.1785</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.3603</v>
+        <v>0.1785</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7698</v>
+        <v>-1.403</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1473</v>
+        <v>-1.8876</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3775</v>
+        <v>0.4846</v>
       </c>
       <c r="G12" t="n">
         <v>0.0743</v>
@@ -1390,13 +1390,13 @@
         <v>0.386</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3001</v>
+        <v>0.0668</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.238</v>
+        <v>0.0218</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0621</v>
+        <v>0.0449</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>28.9452</v>
+        <v>29.2424</v>
       </c>
       <c r="E13" t="n">
-        <v>23.7338</v>
+        <v>24.0312</v>
       </c>
       <c r="F13" t="n">
         <v>5.2111</v>
       </c>
       <c r="G13" t="n">
-        <v>20.3957</v>
+        <v>20.39570000000001</v>
       </c>
       <c r="H13" t="n">
         <v>19.0284</v>
@@ -1456,10 +1456,10 @@
         <v>1.3318</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.6303</v>
+        <v>-5.630300000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.8253</v>
+        <v>-4.825299999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.4406</v>
@@ -1468,19 +1468,19 @@
         <v>10.6154</v>
       </c>
       <c r="S13" t="n">
-        <v>12.3999</v>
+        <v>12.6977</v>
       </c>
       <c r="T13" t="n">
-        <v>12.0764</v>
+        <v>12.3738</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3236999999999999</v>
+        <v>0.3237000000000002</v>
       </c>
       <c r="V13" t="n">
         <v>0.9745999999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>2.403999999999999</v>
+        <v>2.404</v>
       </c>
       <c r="X13" t="n">
         <v>-1.4294</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>E. CARPINTERO REVILLA</t>
+          <t>A. REY GUTIERREZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,40 +1501,40 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.2465</v>
+        <v>2.0789</v>
       </c>
       <c r="E14" t="n">
-        <v>3.119</v>
+        <v>1.2946</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.8725000000000001</v>
+        <v>0.7843</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4859</v>
+        <v>1.1946</v>
       </c>
       <c r="H14" t="n">
-        <v>0.383</v>
+        <v>0.4927</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1028</v>
+        <v>0.7019</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1028</v>
+        <v>1.4482</v>
       </c>
       <c r="K14" t="n">
-        <v>2.9807</v>
+        <v>1.4075</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1221</v>
+        <v>0.0407</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.6169</v>
+        <v>-0.2537</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.5976</v>
+        <v>-0.9149</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0193</v>
+        <v>0.6612</v>
       </c>
       <c r="P14" t="n">
         <v>1.3511</v>
@@ -1546,28 +1546,28 @@
         <v>1.3511</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8606</v>
+        <v>-0.509</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2697</v>
+        <v>-0.1537</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.591</v>
+        <v>-0.3553</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2702</v>
+        <v>0.0422</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9843</v>
+        <v>0.0422</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. REY GUTIERREZ</t>
+          <t>E. CARPINTERO REVILLA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,40 +1579,40 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0584</v>
+        <v>1.9121</v>
       </c>
       <c r="E15" t="n">
-        <v>1.595</v>
+        <v>2.9187</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4634</v>
+        <v>-1.0067</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1946</v>
+        <v>0.4859</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4927</v>
+        <v>0.383</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7019</v>
+        <v>0.1028</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4482</v>
+        <v>3.1028</v>
       </c>
       <c r="K15" t="n">
-        <v>1.4075</v>
+        <v>2.9807</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0407</v>
+        <v>0.1221</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.2537</v>
+        <v>-2.6169</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.9149</v>
+        <v>-2.5976</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6612</v>
+        <v>-0.0193</v>
       </c>
       <c r="P15" t="n">
         <v>1.3511</v>
@@ -1624,22 +1624,22 @@
         <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5294</v>
+        <v>-1.1951</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1468</v>
+        <v>-0.4699</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6762</v>
+        <v>-0.7251</v>
       </c>
       <c r="V15" t="n">
-        <v>0.0422</v>
+        <v>1.2702</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0422</v>
+        <v>0.9843</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4491</v>
+        <v>1.1431</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0633</v>
+        <v>1.8644</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6142</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="G16" t="n">
         <v>0.9385</v>
@@ -1702,13 +1702,13 @@
         <v>1.158</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3616</v>
+        <v>-0.6676</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4759</v>
+        <v>0.3252</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8857</v>
+        <v>-0.9928</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2859</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. NDOYE</t>
+          <t>A. LOPEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7082</v>
+        <v>-1.7093</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1299</v>
+        <v>-2.6193</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8381</v>
+        <v>0.91</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.7551</v>
+        <v>-1.0857</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-1.6198</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9654</v>
+        <v>0.5341</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2402</v>
+        <v>-1.2524</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3623</v>
+        <v>-1.2524</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1221</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5149</v>
+        <v>0.1667</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4274</v>
+        <v>-0.3674</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0875</v>
+        <v>0.5341</v>
       </c>
       <c r="P17" t="n">
-        <v>0.193</v>
+        <v>-0.193</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.965</v>
       </c>
       <c r="R17" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.1461</v>
+        <v>-0.4306</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3702</v>
+        <v>-0.4019</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5162</v>
+        <v>-0.0288</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. LOPEZ FERNANDEZ</t>
+          <t>N. NDOYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.709</v>
+        <v>-2.082</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.6193</v>
+        <v>-0.2706</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9103</v>
+        <v>-1.8113</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0857</v>
+        <v>-1.7551</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6198</v>
+        <v>-0.7897999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5341</v>
+        <v>-0.9654</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.2524</v>
+        <v>-0.2402</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.2524</v>
+        <v>-0.3623</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1221</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1667</v>
+        <v>-1.5149</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.3674</v>
+        <v>-0.4274</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5341</v>
+        <v>-1.0875</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.193</v>
+        <v>0.193</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.965</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4303</v>
+        <v>-0.5199</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4019</v>
+        <v>-0.0304</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0284</v>
+        <v>-0.4895</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. HERNANDEZ HERNANDEZ</t>
+          <t>J. PATERNINA ARBIDE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9399</v>
+        <v>-3.0642</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4089</v>
+        <v>-0.885</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3489</v>
+        <v>-2.1792</v>
       </c>
       <c r="G19" t="n">
-        <v>-6.2805</v>
+        <v>-1.7857</v>
       </c>
       <c r="H19" t="n">
-        <v>-5.6379</v>
+        <v>-0.0828</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-1.7029</v>
       </c>
       <c r="J19" t="n">
-        <v>-3.1038</v>
+        <v>0.7169</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.3073</v>
+        <v>1.3195</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2035</v>
+        <v>-0.6026</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.1767</v>
+        <v>-2.5026</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.3306</v>
+        <v>-1.4023</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8461</v>
+        <v>-1.1003</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3511</v>
+        <v>-0</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.965</v>
       </c>
       <c r="R19" t="n">
-        <v>2.3161</v>
+        <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7616</v>
+        <v>-1.3629</v>
       </c>
       <c r="T19" t="n">
-        <v>2.9639</v>
+        <v>-0.6368</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.2024</v>
+        <v>-0.7261</v>
       </c>
       <c r="V19" t="n">
-        <v>1.228</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2859</v>
+        <v>0.08450000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PATERNINA ARBIDE</t>
+          <t>O. HERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5249</v>
+        <v>-3.5356</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1854</v>
+        <v>-1.2935</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3395</v>
+        <v>-2.2421</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.7857</v>
+        <v>-6.2805</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0828</v>
+        <v>-5.6379</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7029</v>
+        <v>-0.6425999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7169</v>
+        <v>-3.1038</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3195</v>
+        <v>-3.3073</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6026</v>
+        <v>0.2035</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5026</v>
+        <v>-3.1767</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4023</v>
+        <v>-2.3306</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.1003</v>
+        <v>-0.8461</v>
       </c>
       <c r="P20" t="n">
-        <v>-0</v>
+        <v>1.3511</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.965</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>2.3161</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.8237</v>
+        <v>0.1659</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9373</v>
+        <v>1.2615</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8864</v>
+        <v>-1.0956</v>
       </c>
       <c r="V20" t="n">
-        <v>0.08450000000000001</v>
+        <v>1.228</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X20" t="n">
-        <v>0.08450000000000001</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0373</v>
+        <v>-4.0025</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4165</v>
+        <v>-0.5153</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.6207</v>
+        <v>-3.4872</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0926</v>
@@ -2092,13 +2092,13 @@
         <v>1.158</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.9446</v>
+        <v>-0.9098000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9373</v>
+        <v>-0.036</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0074</v>
+        <v>-0.8739</v>
       </c>
       <c r="V21" t="n">
         <v>-1.228</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.3086</v>
+        <v>-5.0347</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0252</v>
+        <v>-0.07489999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-5.3338</v>
+        <v>-4.9597</v>
       </c>
       <c r="G22" t="n">
         <v>-4.4993</v>
@@ -2170,13 +2170,13 @@
         <v>2.7021</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2606</v>
+        <v>-1.9866</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4852</v>
+        <v>0.3851</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.7458</v>
+        <v>-2.3717</v>
       </c>
       <c r="V22" t="n">
         <v>-0.2859</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.1881</v>
+        <v>-5.7003</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3544</v>
+        <v>-3.0539</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8337</v>
+        <v>-2.6464</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8941</v>
@@ -2248,13 +2248,13 @@
         <v>0.965</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0431</v>
+        <v>-1.5553</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8923</v>
+        <v>-0.5919</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1508</v>
+        <v>-0.9634</v>
       </c>
       <c r="V23" t="n">
         <v>-0.2859</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.283099999999999</v>
+        <v>-7.6155</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.9769</v>
+        <v>-2.5763</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.3062</v>
+        <v>-5.0392</v>
       </c>
       <c r="G24" t="n">
         <v>-3.6217</v>
@@ -2326,13 +2326,13 @@
         <v>2.5091</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.7616</v>
+        <v>-2.094</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3754</v>
+        <v>0.0252</v>
       </c>
       <c r="U24" t="n">
-        <v>-2.3862</v>
+        <v>-2.1192</v>
       </c>
       <c r="V24" t="n">
         <v>-1.5138</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-28.9451</v>
+        <v>-27.61</v>
       </c>
       <c r="E25" t="n">
-        <v>-5.2112</v>
+        <v>-5.2111</v>
       </c>
       <c r="F25" t="n">
-        <v>-23.7339</v>
+        <v>-22.3988</v>
       </c>
       <c r="G25" t="n">
         <v>-20.3957</v>
@@ -2374,10 +2374,10 @@
         <v>-19.0285</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3673</v>
+        <v>-1.367300000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>4.298399999999999</v>
+        <v>4.2984</v>
       </c>
       <c r="K25" t="n">
         <v>-1.3317</v>
@@ -2395,7 +2395,7 @@
         <v>-6.9974</v>
       </c>
       <c r="P25" t="n">
-        <v>4.8254</v>
+        <v>4.825399999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-10.6153</v>
@@ -2404,13 +2404,13 @@
         <v>15.4405</v>
       </c>
       <c r="S25" t="n">
-        <v>-12.4</v>
+        <v>-11.0649</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3236999999999998</v>
+        <v>-0.3235999999999999</v>
       </c>
       <c r="U25" t="n">
-        <v>-12.0765</v>
+        <v>-10.7414</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9746000000000001</v>
